--- a/output/pdf_financials_xlsx/AIR.xlsx
+++ b/output/pdf_financials_xlsx/AIR.xlsx
@@ -4536,37 +4536,37 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.749897</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.749897</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.749897</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.749897</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.902457</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.696021</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>9.081593</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>14.037838</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>14.144981</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>14.355624</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>14.429863</v>
       </c>
     </row>
     <row r="93">
@@ -7468,7 +7468,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10062,7 +10066,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -11116,7 +11124,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -11490,7 +11502,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -11950,7 +11966,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AIR.xlsx
+++ b/output/pdf_financials_xlsx/AIR.xlsx
@@ -915,22 +915,22 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.063985</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.048945</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.062899</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.390713</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.206585</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.070536</v>
       </c>
     </row>
     <row r="13">
@@ -1640,22 +1640,22 @@
         <v>-1.135819</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.273525</v>
+        <v>-1.33751</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.032832</v>
+        <v>-2.081777</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.954873</v>
+        <v>-5.017772</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.529771</v>
+        <v>-3.920484</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.124992</v>
+        <v>-3.331577</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.361118</v>
+        <v>-1.431654</v>
       </c>
     </row>
     <row r="28">
@@ -1730,22 +1730,22 @@
         <v>-1.135819</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.264482</v>
+        <v>-1.328467</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.01333</v>
+        <v>-2.062275</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.932802</v>
+        <v>-4.995701</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.508927</v>
+        <v>-3.89964</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.11017</v>
+        <v>-3.316755</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.349602</v>
+        <v>-1.420138</v>
       </c>
     </row>
     <row r="30">
@@ -1941,40 +1941,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.062622</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.015287</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.005387</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.007121</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.704747</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.547073</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.678356</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.542573</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.871401</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.913395</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.441879</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.133766</v>
       </c>
     </row>
     <row r="35">
@@ -2027,40 +2027,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.062622</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.015287</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.005387</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.007121</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.704747</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.547073</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6.678356</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.542573</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.871401</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.913395</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.441879</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.133766</v>
       </c>
     </row>
     <row r="37">
@@ -2543,40 +2543,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.062622</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.015287</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.005387</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.007121</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.704747</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.961497</v>
+        <v>0.414424</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>7.585944</v>
+        <v>0.907588</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.318291</v>
+        <v>0.775718</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.308331</v>
+        <v>0.43693</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>6.560021</v>
+        <v>0.646626</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.201865</v>
+        <v>0.7599860000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.340625</v>
+        <v>0.206859</v>
       </c>
     </row>
     <row r="49">
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02132</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.025699</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.021394</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008418</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>0</v>
@@ -6003,16 +6003,16 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02132</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.025699</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.021394</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008418</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>0</v>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -14024,7 +14024,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -20430,7 +20434,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -21224,7 +21228,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -22594,7 +22598,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -22674,7 +22678,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -23518,7 +23522,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">

--- a/output/pdf_financials_xlsx/AIR.xlsx
+++ b/output/pdf_financials_xlsx/AIR.xlsx
@@ -1694,10 +1694,10 @@
         <v>0.022071</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.020844</v>
+        <v>0.017357</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.014822</v>
+        <v>0.0055</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0.011516</v>
@@ -1739,10 +1739,10 @@
         <v>-4.995701</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.89964</v>
+        <v>-3.903127</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.316755</v>
+        <v>-3.326077</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.420138</v>
@@ -4882,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.017357</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
@@ -13174,7 +13174,11 @@
           <t>Depreciation – right of use asset</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AIR.xlsx
+++ b/output/pdf_financials_xlsx/AIR.xlsx
@@ -534,10 +534,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -579,10 +577,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -624,10 +620,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -669,10 +663,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.032423</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.073019</v>
@@ -714,10 +706,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -759,10 +749,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.001954</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.008267</v>
@@ -804,10 +792,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.104859</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.081286</v>
@@ -849,10 +835,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.104859</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.097496</v>
@@ -894,10 +878,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -939,10 +921,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -984,10 +964,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -1029,10 +1007,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -1074,10 +1050,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.151034</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.097496</v>
@@ -1119,10 +1093,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1146,7 +1118,7 @@
         <v>0.138</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.138</v>
+        <v>-0.138</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -1298,10 +1270,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.151034</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.097496</v>
@@ -1343,10 +1313,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1388,10 +1356,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1433,10 +1399,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.151034</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.097496</v>
@@ -1619,10 +1583,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.151034</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.097496</v>
@@ -1664,10 +1626,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1709,10 +1669,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.151034</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.097496</v>
@@ -1821,10 +1779,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -3404,40 +3360,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.144528</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.240698</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.125829</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.238149</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.077706</v>
       </c>
     </row>
     <row r="68">
@@ -3447,40 +3403,40 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.059343</v>
+        <v>0.069343</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.139313</v>
+        <v>0.146813</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.18972</v>
+        <v>0.19472</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.251986</v>
+        <v>0.258486</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.036131</v>
+        <v>0.043631</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.441791</v>
+        <v>0.586319</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.230805</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.90543</v>
+        <v>0.95543</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.6093190000000001</v>
+        <v>0.850017</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.125829</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.238149</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.077706</v>
       </c>
     </row>
     <row r="69">
@@ -3751,31 +3707,31 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.015</v>
+        <v>0.0075</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.048886</v>
+        <v>0.043886</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.089851</v>
+        <v>0.08335099999999999</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.001323</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.251323</v>
+        <v>0.106795</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>1.692799</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.04496</v>
+        <v>1.99496</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.014335</v>
+        <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>3.478961</v>
+        <v>3.353132</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>0</v>
@@ -4807,10 +4763,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.151034</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.097496</v>
@@ -4852,10 +4806,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -4897,10 +4849,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.0005509999999999999</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.000737</v>
@@ -4918,22 +4868,22 @@
         <v>0</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.494369</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.092779</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-5</v>
+        <v>-4.681449</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>4.879161</v>
+        <v>4.508792</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.120839</v>
+        <v>-0.08340400000000001</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.539214</v>
       </c>
     </row>
     <row r="102">
@@ -4942,10 +4892,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -4987,10 +4935,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -5032,10 +4978,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.020134</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.056914</v>
@@ -5077,10 +5021,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -5122,10 +5064,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.019583</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.056177</v>
@@ -5143,22 +5083,22 @@
         <v>0.058775</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.397973</v>
+        <v>-0.892342</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.701214</v>
+        <v>0.7939929999999999</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-5.494048</v>
+        <v>-5.175497</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>4.542451</v>
+        <v>4.172082</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.350055</v>
+        <v>0.145812</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.255076</v>
+        <v>0.284138</v>
       </c>
     </row>
     <row r="107">
@@ -5167,10 +5107,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -5212,10 +5150,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -5257,10 +5193,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -5302,10 +5236,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -5347,10 +5279,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -5392,10 +5322,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5437,10 +5365,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -5482,10 +5408,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -5527,10 +5451,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -5572,10 +5494,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -5617,10 +5537,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -5662,10 +5580,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0.046175</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -5707,10 +5623,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>0</v>
@@ -5754,10 +5668,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -5799,10 +5711,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -5844,10 +5754,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -5889,10 +5797,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -5934,10 +5840,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -5979,10 +5883,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -6024,10 +5926,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -6136,10 +6036,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -6181,10 +6079,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.1025</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.015</v>
@@ -6232,10 +6128,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.045398</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.041606</v>
@@ -6277,10 +6171,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -6322,10 +6214,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.017224</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.026319</v>
@@ -6367,10 +6257,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.062622</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.015287</v>
@@ -6412,10 +6300,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -6457,10 +6343,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.085276</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.041319</v>
@@ -6513,7 +6397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P244"/>
+  <dimension ref="A1:P267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13462,7 +13346,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -14176,7 +14064,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -14570,7 +14462,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -14778,7 +14674,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -19413,24 +19313,18 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Accretion interest (Note 8) $</t>
+          <t>For the years ended January</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E175" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19457,20 +19351,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K175" s="5" t="n">
-        <v>0.164244</v>
-      </c>
-      <c r="L175" s="5" t="n">
-        <v>0.368003</v>
-      </c>
-      <c r="M175" s="5" t="n">
-        <v>0.766033</v>
-      </c>
-      <c r="N175" s="5" t="n">
-        <v>0.503045</v>
-      </c>
-      <c r="O175" s="5" t="n">
-        <v>0.206747</v>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
@@ -19481,28 +19385,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss and comprehensive loss for the year $ (94,133) $</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" s="5" t="n">
+        <v>-0.151034</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19544,41 +19442,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N176" s="5" t="n">
-        <v>0.103572</v>
-      </c>
-      <c r="O176" s="5" t="n">
-        <v>0.146171</v>
-      </c>
-      <c r="P176" s="5" t="n">
-        <v>0.136009</v>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Depreciation (Note 4)</t>
+          <t>Write-off of exploration and evaluation assets -</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="n">
+        <v>0.046175</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19605,50 +19507,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K177" s="5" t="n">
-        <v>0.009043000000000001</v>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v>0.019502</v>
-      </c>
-      <c r="M177" s="5" t="n">
-        <v>0.022071</v>
-      </c>
-      <c r="N177" s="5" t="n">
-        <v>0.020844</v>
-      </c>
-      <c r="O177" s="5" t="n">
-        <v>0.014822</v>
-      </c>
-      <c r="P177" s="5" t="n">
-        <v>0.011516</v>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Receivables 61</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="n">
+        <v>-0.0005509999999999999</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19675,46 +19587,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K178" s="5" t="n">
-        <v>0.01962</v>
-      </c>
-      <c r="L178" s="5" t="n">
-        <v>0.031928</v>
-      </c>
-      <c r="M178" s="5" t="n">
-        <v>0.049859</v>
-      </c>
-      <c r="N178" s="5" t="n">
-        <v>0.062234</v>
-      </c>
-      <c r="O178" s="5" t="n">
-        <v>0.027437</v>
-      </c>
-      <c r="P178" s="5" t="n">
-        <v>0.032731</v>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Investor relations and marketing</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Trade and other payables 23,056</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>0.020134</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19741,46 +19667,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K179" s="5" t="n">
-        <v>0.602668</v>
-      </c>
-      <c r="L179" s="5" t="n">
-        <v>0.64472</v>
-      </c>
-      <c r="M179" s="5" t="n">
-        <v>0.958148</v>
-      </c>
-      <c r="N179" s="5" t="n">
-        <v>0.560318</v>
-      </c>
-      <c r="O179" s="5" t="n">
-        <v>0.33027</v>
-      </c>
-      <c r="P179" s="5" t="n">
-        <v>0.152617</v>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Office, administration and rent</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash Flows Used in Operating Activities (71,016)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="n">
+        <v>-0.085276</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19807,106 +19747,140 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K180" s="5" t="n">
-        <v>0.127723</v>
-      </c>
-      <c r="L180" s="5" t="n">
-        <v>0.07469000000000001</v>
-      </c>
-      <c r="M180" s="5" t="n">
-        <v>0.094026</v>
-      </c>
-      <c r="N180" s="5" t="n">
-        <v>0.059426</v>
-      </c>
-      <c r="O180" s="5" t="n">
-        <v>0.06426999999999999</v>
-      </c>
-      <c r="P180" s="5" t="n">
-        <v>0.04175</v>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Shares issued for cash 50,000</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>0.012281</v>
-      </c>
-      <c r="G181" s="5" t="n">
-        <v>0.009874000000000001</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>0.01209</v>
-      </c>
-      <c r="I181" s="5" t="n">
-        <v>0.009864</v>
-      </c>
-      <c r="J181" s="5" t="n">
-        <v>0.114886</v>
-      </c>
-      <c r="K181" s="5" t="n">
-        <v>0.183562</v>
-      </c>
-      <c r="L181" s="5" t="n">
-        <v>0.385578</v>
-      </c>
-      <c r="M181" s="5" t="n">
-        <v>0.563277</v>
-      </c>
-      <c r="N181" s="5" t="n">
-        <v>0.336903</v>
-      </c>
-      <c r="O181" s="5" t="n">
-        <v>0.144278</v>
-      </c>
-      <c r="P181" s="5" t="n">
-        <v>0.129462</v>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 9 and 11)</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash Flows Provided by Financing Activities 50,000</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>0.1025</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19948,213 +19922,277 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N182" s="5" t="n">
-        <v>0.394913</v>
-      </c>
-      <c r="O182" s="5" t="n">
-        <v>0.206657</v>
-      </c>
-      <c r="P182" s="5" t="n">
-        <v>0.078614</v>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Shareholder relations</t>
+          <t>Change in Cash for the Year (21,016)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F183" s="5" t="n">
-        <v>0.003929</v>
+      <c r="E183" s="5" t="n">
+        <v>0.017224</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H183" s="5" t="n">
-        <v>0.012423</v>
-      </c>
-      <c r="I183" s="5" t="n">
-        <v>0.008116999999999999</v>
-      </c>
-      <c r="J183" s="5" t="n">
-        <v>0.011036</v>
-      </c>
-      <c r="K183" s="5" t="n">
-        <v>0.011978</v>
-      </c>
-      <c r="L183" s="5" t="n">
-        <v>0.00405</v>
-      </c>
-      <c r="M183" s="5" t="n">
-        <v>0.003057</v>
-      </c>
-      <c r="N183" s="5" t="n">
-        <v>0.003263</v>
-      </c>
-      <c r="O183" s="5" t="n">
-        <v>0.012655</v>
-      </c>
-      <c r="P183" s="5" t="n">
-        <v>0.031029</v>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Cash, Beginning of Year 62,622</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F184" s="5" t="n">
-        <v>0.025019</v>
-      </c>
-      <c r="G184" s="5" t="n">
-        <v>0.033145</v>
-      </c>
-      <c r="H184" s="5" t="n">
-        <v>0.020989</v>
-      </c>
-      <c r="I184" s="5" t="n">
-        <v>0.016618</v>
-      </c>
-      <c r="J184" s="5" t="n">
-        <v>0.03355</v>
-      </c>
-      <c r="K184" s="5" t="n">
-        <v>0.047553</v>
-      </c>
-      <c r="L184" s="5" t="n">
-        <v>0.045387</v>
-      </c>
-      <c r="M184" s="5" t="n">
-        <v>0.078842</v>
-      </c>
-      <c r="N184" s="5" t="n">
-        <v>0.070205</v>
-      </c>
-      <c r="O184" s="5" t="n">
-        <v>0.066578</v>
-      </c>
-      <c r="P184" s="5" t="n">
-        <v>0.071233</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="n">
+        <v>0.045398</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Travel and entertainment</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, End of Year $ 41,606 $</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n">
+        <v>0.062622</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G185" s="5" t="n">
-        <v>0.001859</v>
-      </c>
-      <c r="H185" s="5" t="n">
-        <v>0.004681</v>
-      </c>
-      <c r="I185" s="5" t="n">
-        <v>0.006913</v>
-      </c>
-      <c r="J185" s="5" t="n">
-        <v>0.01209</v>
-      </c>
-      <c r="K185" s="5" t="n">
-        <v>0.044363</v>
-      </c>
-      <c r="L185" s="5" t="n">
-        <v>0.021084</v>
-      </c>
-      <c r="M185" s="5" t="n">
-        <v>0.133946</v>
-      </c>
-      <c r="N185" s="5" t="n">
-        <v>0.068743</v>
-      </c>
-      <c r="O185" s="5" t="n">
-        <v>0.102805</v>
-      </c>
-      <c r="P185" s="5" t="n">
-        <v>0.080958</v>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wages and benefits (Note 11)</t>
+          <t>Shares issued for debt $ - $</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E186" s="5" t="n">
+        <v>0.154078</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20196,37 +20234,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N186" s="5" t="n">
-        <v>1.747318</v>
-      </c>
-      <c r="O186" s="5" t="n">
-        <v>2.193148</v>
-      </c>
-      <c r="P186" s="5" t="n">
-        <v>0.819839</v>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Loss before income taxes and other Items</t>
+          <t>Allocation of subscriptions received in advance $ - $</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E187" s="5" t="n">
+        <v>0.105</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20253,23 +20295,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K187" s="5" t="n">
-        <v>-3.535976</v>
-      </c>
-      <c r="L187" s="5" t="n">
-        <v>-3.405191</v>
-      </c>
-      <c r="M187" s="5" t="n">
-        <v>-5.565889</v>
-      </c>
-      <c r="N187" s="5" t="n">
-        <v>-3.930784</v>
-      </c>
-      <c r="O187" s="5" t="n">
-        <v>-3.515838</v>
-      </c>
-      <c r="P187" s="5" t="n">
-        <v>-1.585758</v>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -20280,12 +20334,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Flow-through share premium (Note 9 and 10)</t>
+          <t>Accretion interest (Note 8) $</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -20319,31 +20373,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K188" s="5" t="n">
+        <v>0.164244</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>0.368003</v>
+      </c>
+      <c r="M188" s="5" t="n">
+        <v>0.766033</v>
+      </c>
+      <c r="N188" s="5" t="n">
+        <v>0.503045</v>
       </c>
       <c r="O188" s="5" t="n">
-        <v>0.180861</v>
-      </c>
-      <c r="P188" s="5" t="n">
-        <v>0.154104</v>
+        <v>0.206747</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -20354,15 +20402,19 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Gain on sale of equipment (Note 4)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Consulting fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -20409,15 +20461,13 @@
         </is>
       </c>
       <c r="N189" s="5" t="n">
-        <v>0.0103</v>
+        <v>0.103572</v>
       </c>
       <c r="O189" s="5" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.146171</v>
+      </c>
+      <c r="P189" s="5" t="n">
+        <v>0.136009</v>
       </c>
     </row>
     <row r="190">
@@ -20428,17 +20478,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Depreciation (Note 4)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -20472,22 +20522,22 @@
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>0.063985</v>
+        <v>0.009043000000000001</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>0.048945</v>
+        <v>0.019502</v>
       </c>
       <c r="M190" s="5" t="n">
-        <v>0.062899</v>
+        <v>0.022071</v>
       </c>
       <c r="N190" s="5" t="n">
-        <v>0.390713</v>
+        <v>0.020844</v>
       </c>
       <c r="O190" s="5" t="n">
-        <v>0.206585</v>
+        <v>0.014822</v>
       </c>
       <c r="P190" s="5" t="n">
-        <v>0.070536</v>
+        <v>0.011516</v>
       </c>
     </row>
     <row r="191">
@@ -20498,15 +20548,19 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Other Items total</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -20537,25 +20591,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K191" s="5" t="n">
+        <v>0.01962</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>1.372359</v>
+        <v>0.031928</v>
       </c>
       <c r="M191" s="5" t="n">
-        <v>0.611016</v>
+        <v>0.049859</v>
       </c>
       <c r="N191" s="5" t="n">
-        <v>0.401013</v>
+        <v>0.062234</v>
       </c>
       <c r="O191" s="5" t="n">
-        <v>0.390846</v>
+        <v>0.027437</v>
       </c>
       <c r="P191" s="5" t="n">
-        <v>1.361118</v>
+        <v>0.032731</v>
       </c>
     </row>
     <row r="192">
@@ -20566,19 +20618,15 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Investor relations and marketing</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -20609,25 +20657,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K192" s="5" t="n">
+        <v>0.602668</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>-2.170832</v>
+        <v>0.64472</v>
       </c>
       <c r="M192" s="5" t="n">
-        <v>-4.816873</v>
+        <v>0.958148</v>
       </c>
       <c r="N192" s="5" t="n">
-        <v>-3.529771</v>
+        <v>0.560318</v>
       </c>
       <c r="O192" s="5" t="n">
-        <v>-3.124992</v>
+        <v>0.33027</v>
       </c>
       <c r="P192" s="5" t="n">
-        <v>-1.361118</v>
+        <v>0.152617</v>
       </c>
     </row>
     <row r="193">
@@ -20638,19 +20684,15 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Office, administration and rent</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -20681,25 +20723,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K193" s="5" t="n">
+        <v>0.127723</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.07469000000000001</v>
       </c>
       <c r="M193" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.094026</v>
       </c>
       <c r="N193" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.059426</v>
       </c>
       <c r="O193" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.06426999999999999</v>
       </c>
       <c r="P193" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.04175</v>
       </c>
     </row>
     <row r="194">
@@ -20710,17 +20750,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -20728,50 +20768,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F194" s="5" t="n">
+        <v>0.012281</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>0.009874000000000001</v>
+      </c>
+      <c r="H194" s="5" t="n">
+        <v>0.01209</v>
+      </c>
+      <c r="I194" s="5" t="n">
+        <v>0.009864</v>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>0.114886</v>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>0.183562</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>131.710164</v>
+        <v>0.385578</v>
       </c>
       <c r="M194" s="5" t="n">
-        <v>219.591324</v>
+        <v>0.563277</v>
       </c>
       <c r="N194" s="5" t="n">
-        <v>223.843153</v>
+        <v>0.336903</v>
       </c>
       <c r="O194" s="5" t="n">
-        <v>230.892409</v>
+        <v>0.144278</v>
       </c>
       <c r="P194" s="5" t="n">
-        <v>250.556784</v>
+        <v>0.129462</v>
       </c>
     </row>
     <row r="195">
@@ -20782,19 +20810,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 9 and 11)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -20830,22 +20854,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L195" s="5" t="n">
-        <v>-2.032832</v>
-      </c>
-      <c r="M195" s="5" t="n">
-        <v>-4.954873</v>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N195" s="5" t="n">
-        <v>-3.529771</v>
+        <v>0.394913</v>
       </c>
       <c r="O195" s="5" t="n">
-        <v>-3.124992</v>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.206657</v>
+      </c>
+      <c r="P195" s="5" t="n">
+        <v>0.078614</v>
       </c>
     </row>
     <row r="196">
@@ -20861,63 +20887,49 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Shareholder relations</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F196" s="5" t="n">
+        <v>0.003929</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H196" s="5" t="n">
+        <v>0.012423</v>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>0.008116999999999999</v>
       </c>
       <c r="J196" s="5" t="n">
-        <v>0.079613</v>
+        <v>0.011036</v>
       </c>
       <c r="K196" s="5" t="n">
-        <v>0.18741</v>
+        <v>0.011978</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>0.096</v>
+        <v>0.00405</v>
       </c>
       <c r="M196" s="5" t="n">
-        <v>0.1008</v>
+        <v>0.003057</v>
       </c>
       <c r="N196" s="5" t="n">
-        <v>0.103572</v>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003263</v>
+      </c>
+      <c r="O196" s="5" t="n">
+        <v>0.012655</v>
+      </c>
+      <c r="P196" s="5" t="n">
+        <v>0.031029</v>
       </c>
     </row>
     <row r="197">
@@ -20933,65 +20945,51 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 9 and 10)</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F197" s="5" t="n">
+        <v>0.025019</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>0.033145</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>0.020989</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>0.016618</v>
+      </c>
+      <c r="J197" s="5" t="n">
+        <v>0.03355</v>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>0.047553</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>0.045387</v>
       </c>
       <c r="M197" s="5" t="n">
-        <v>1.210277</v>
+        <v>0.078842</v>
       </c>
       <c r="N197" s="5" t="n">
-        <v>0.394913</v>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.070205</v>
+      </c>
+      <c r="O197" s="5" t="n">
+        <v>0.066578</v>
+      </c>
+      <c r="P197" s="5" t="n">
+        <v>0.071233</v>
       </c>
     </row>
     <row r="198">
@@ -21007,7 +21005,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Wages and benefits (Note 10)</t>
+          <t>Travel and entertainment</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -21021,47 +21019,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G198" s="5" t="n">
+        <v>0.001859</v>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>0.004681</v>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>0.006913</v>
+      </c>
+      <c r="J198" s="5" t="n">
+        <v>0.01209</v>
       </c>
       <c r="K198" s="5" t="n">
-        <v>1.045559</v>
+        <v>0.044363</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>1.329066</v>
+        <v>0.021084</v>
       </c>
       <c r="M198" s="5" t="n">
-        <v>1.585553</v>
+        <v>0.133946</v>
       </c>
       <c r="N198" s="5" t="n">
-        <v>1.747318</v>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.068743</v>
+      </c>
+      <c r="O198" s="5" t="n">
+        <v>0.102805</v>
+      </c>
+      <c r="P198" s="5" t="n">
+        <v>0.080958</v>
       </c>
     </row>
     <row r="199">
@@ -21072,12 +21058,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Flow-through share premium (Note 9)</t>
+          <t>Wages and benefits (Note 11)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -21116,26 +21102,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L199" s="5" t="n">
-        <v>1.331629</v>
-      </c>
-      <c r="M199" s="5" t="n">
-        <v>0.393863</v>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="5" t="n">
+        <v>1.747318</v>
+      </c>
+      <c r="O199" s="5" t="n">
+        <v>2.193148</v>
+      </c>
+      <c r="P199" s="5" t="n">
+        <v>0.819839</v>
       </c>
     </row>
     <row r="200">
@@ -21146,12 +21130,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Gain on sale of asset (Note 4)</t>
+          <t>Loss before income taxes and other Items</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -21185,33 +21169,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K200" s="5" t="n">
+        <v>-3.535976</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>-3.405191</v>
+      </c>
+      <c r="M200" s="5" t="n">
+        <v>-5.565889</v>
       </c>
       <c r="N200" s="5" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.930784</v>
+      </c>
+      <c r="O200" s="5" t="n">
+        <v>-3.515838</v>
+      </c>
+      <c r="P200" s="5" t="n">
+        <v>-1.585758</v>
       </c>
     </row>
     <row r="201">
@@ -21227,14 +21201,10 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Flow-through share premium (Note 9 and 10)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -21265,29 +21235,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K201" s="5" t="n">
-        <v>-0.012534</v>
-      </c>
-      <c r="L201" s="5" t="n">
-        <v>-0.0125</v>
-      </c>
-      <c r="M201" s="5" t="n">
-        <v>-0.003048</v>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O201" s="5" t="n">
+        <v>0.180861</v>
+      </c>
+      <c r="P201" s="5" t="n">
+        <v>0.154104</v>
       </c>
     </row>
     <row r="202">
@@ -21303,14 +21275,10 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain on sale of equipment (Note 4)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -21346,21 +21314,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L202" s="5" t="n">
-        <v>0.004285</v>
-      </c>
-      <c r="M202" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="5" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="O202" s="5" t="n">
+        <v>0.0034</v>
       </c>
       <c r="P202" t="inlineStr">
         <is>
@@ -21381,10 +21349,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Settlement of note payable (Note 8(a))</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -21415,33 +21387,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K203" s="5" t="n">
+        <v>0.063985</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>0.048945</v>
       </c>
       <c r="M203" s="5" t="n">
-        <v>0.149302</v>
-      </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.062899</v>
+      </c>
+      <c r="N203" s="5" t="n">
+        <v>0.390713</v>
+      </c>
+      <c r="O203" s="5" t="n">
+        <v>0.206585</v>
+      </c>
+      <c r="P203" s="5" t="n">
+        <v>0.070536</v>
       </c>
     </row>
     <row r="204">
@@ -21457,7 +21419,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (expense) (Note 16)</t>
+          <t>Other Items total</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -21496,28 +21458,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L204" s="5" t="n">
+        <v>1.372359</v>
       </c>
       <c r="M204" s="5" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.611016</v>
+      </c>
+      <c r="N204" s="5" t="n">
+        <v>0.401013</v>
+      </c>
+      <c r="O204" s="5" t="n">
+        <v>0.390846</v>
+      </c>
+      <c r="P204" s="5" t="n">
+        <v>1.361118</v>
       </c>
     </row>
     <row r="205">
@@ -21528,15 +21482,19 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 9)</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -21562,32 +21520,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J205" s="5" t="n">
-        <v>0.15256</v>
-      </c>
-      <c r="K205" s="5" t="n">
-        <v>1.081268</v>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L205" s="5" t="n">
-        <v>0.385183</v>
+        <v>-2.170832</v>
       </c>
       <c r="M205" s="5" t="n">
-        <v>1.210277</v>
-      </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.816873</v>
+      </c>
+      <c r="N205" s="5" t="n">
+        <v>-3.529771</v>
+      </c>
+      <c r="O205" s="5" t="n">
+        <v>-3.124992</v>
+      </c>
+      <c r="P205" s="5" t="n">
+        <v>-1.361118</v>
       </c>
     </row>
     <row r="206">
@@ -21603,10 +21559,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (expense) (Note 15)</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -21643,25 +21603,19 @@
         </is>
       </c>
       <c r="L206" s="5" t="n">
-        <v>-0.138</v>
+        <v>-2e-08</v>
       </c>
       <c r="M206" s="5" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="N206" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="O206" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="P206" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="207">
@@ -21672,15 +21626,19 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Geological consulting</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -21706,36 +21664,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J207" s="5" t="n">
-        <v>0.31403</v>
-      </c>
-      <c r="K207" s="5" t="n">
-        <v>0.010985</v>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>131.710164</v>
+      </c>
+      <c r="M207" s="5" t="n">
+        <v>219.591324</v>
+      </c>
+      <c r="N207" s="5" t="n">
+        <v>223.843153</v>
+      </c>
+      <c r="O207" s="5" t="n">
+        <v>230.892409</v>
+      </c>
+      <c r="P207" s="5" t="n">
+        <v>250.556784</v>
       </c>
     </row>
     <row r="208">
@@ -21751,10 +21703,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Flow-through share premium</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -21785,26 +21741,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K208" s="5" t="n">
-        <v>2.211</v>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L208" s="5" t="n">
-        <v>1.331629</v>
-      </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.032832</v>
+      </c>
+      <c r="M208" s="5" t="n">
+        <v>-4.954873</v>
+      </c>
+      <c r="N208" s="5" t="n">
+        <v>-3.529771</v>
+      </c>
+      <c r="O208" s="5" t="n">
+        <v>-3.124992</v>
       </c>
       <c r="P208" t="inlineStr">
         <is>
@@ -21820,17 +21772,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Other income (Note 15)</t>
+          <t>Consulting fees (Note 10)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -21858,28 +21810,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J209" s="5" t="n">
+        <v>0.079613</v>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>0.18741</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>0.004285</v>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.096</v>
+      </c>
+      <c r="M209" s="5" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="N209" s="5" t="n">
+        <v>0.103572</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -21900,19 +21844,15 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>1,372,359</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Net loss before income taxes $</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 9 and 10)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -21943,21 +21883,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K210" s="5" t="n">
-        <v>-1.273525</v>
-      </c>
-      <c r="L210" s="5" t="n">
-        <v>-2.032832</v>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" s="5" t="n">
+        <v>1.210277</v>
+      </c>
+      <c r="N210" s="5" t="n">
+        <v>0.394913</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -21978,19 +21918,15 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>1,372,359</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (Note 16)</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Wages and benefits (Note 10)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -22021,23 +21957,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K211" s="5" t="n">
+        <v>1.045559</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>-0.138</v>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.329066</v>
+      </c>
+      <c r="M211" s="5" t="n">
+        <v>1.585553</v>
+      </c>
+      <c r="N211" s="5" t="n">
+        <v>1.747318</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -22058,19 +21988,15 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>1,372,359</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Flow-through share premium (Note 9)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -22101,16 +22027,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K212" s="5" t="n">
-        <v>-1.273525</v>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L212" s="5" t="n">
-        <v>-2.170832</v>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.331629</v>
+      </c>
+      <c r="M212" s="5" t="n">
+        <v>0.393863</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
@@ -22136,19 +22062,15 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>1,372,359</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on sale of asset (Note 4)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -22179,21 +22101,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K213" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L213" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N213" s="5" t="n">
+        <v>0.0103</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -22214,17 +22138,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>1,372,359</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -22258,15 +22182,13 @@
         </is>
       </c>
       <c r="K214" s="5" t="n">
-        <v>106.538916</v>
+        <v>-0.012534</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>131.710164</v>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.0125</v>
+      </c>
+      <c r="M214" s="5" t="n">
+        <v>-0.003048</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
@@ -22292,15 +22214,19 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Legal settlement (Note 13)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -22326,23 +22252,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J215" s="5" t="n">
-        <v>0.25</v>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L215" s="5" t="n">
+        <v>0.004285</v>
+      </c>
+      <c r="M215" s="5" t="n">
+        <v>0.008</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -22368,12 +22292,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Office, admin and rent</t>
+          <t>Settlement of note payable (Note 8(a))</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -22402,21 +22326,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J216" s="5" t="n">
-        <v>0.015657</v>
-      </c>
-      <c r="K216" s="5" t="n">
-        <v>0.127723</v>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M216" s="5" t="n">
+        <v>0.149302</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -22442,15 +22368,19 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Other Items</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>Deferred income tax recovery (expense) (Note 16)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -22476,21 +22406,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J217" s="5" t="n">
-        <v>-0.983422</v>
-      </c>
-      <c r="K217" s="5" t="n">
-        <v>-3.535976</v>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M217" s="5" t="n">
+        <v>0.138</v>
       </c>
       <c r="N217" t="inlineStr">
         <is>
@@ -22521,7 +22453,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Flow-through share premium</t>
+          <t>Share-based compensation (Note 9)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -22550,23 +22482,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J218" s="5" t="n">
+        <v>0.15256</v>
       </c>
       <c r="K218" s="5" t="n">
-        <v>2.211</v>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.081268</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>0.385183</v>
+      </c>
+      <c r="M218" s="5" t="n">
+        <v>1.210277</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -22592,17 +22518,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Deferred income tax recovery (expense) (Note 15)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -22635,18 +22561,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K219" s="5" t="n">
-        <v>0.063985</v>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>-0.138</v>
+      </c>
+      <c r="M219" s="5" t="n">
+        <v>0.138</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
@@ -22677,14 +22601,10 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Geological consulting</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -22711,10 +22631,10 @@
         </is>
       </c>
       <c r="J220" s="5" t="n">
-        <v>-0.002397</v>
+        <v>0.31403</v>
       </c>
       <c r="K220" s="5" t="n">
-        <v>-0.012534</v>
+        <v>0.010985</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -22750,12 +22670,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Loan receivable write-off (Note 13)</t>
+          <t>Flow-through share premium</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -22784,18 +22704,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J221" s="5" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>1.331629</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -22826,17 +22744,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Other income (Note 15)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -22864,16 +22782,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J222" s="5" t="n">
-        <v>-1.135819</v>
-      </c>
-      <c r="K222" s="5" t="n">
-        <v>-1.273525</v>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>0.004285</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -22904,17 +22824,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>1,372,359</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Net loss before income taxes $</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -22942,16 +22862,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J223" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K223" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.273525</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>-2.032832</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
@@ -22982,17 +22902,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>1,372,359</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Deferred income tax expense (Note 16)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -23020,16 +22940,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J224" s="5" t="n">
-        <v>23.596015</v>
-      </c>
-      <c r="K224" s="5" t="n">
-        <v>106.538916</v>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>-0.138</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -23060,17 +22982,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>1,372,359</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 7)</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -23093,21 +23015,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I225" s="5" t="n">
-        <v>0.1425</v>
-      </c>
-      <c r="J225" s="5" t="n">
-        <v>0.079613</v>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>-1.273525</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>-2.170832</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
@@ -23138,17 +23060,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>1,372,359</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Loss per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -23156,30 +23078,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F226" s="5" t="n">
-        <v>0.008267</v>
-      </c>
-      <c r="G226" s="5" t="n">
-        <v>0.004773</v>
-      </c>
-      <c r="H226" s="5" t="n">
-        <v>0.004012</v>
-      </c>
-      <c r="I226" s="5" t="n">
-        <v>0.012454</v>
-      </c>
-      <c r="J226" s="5" t="n">
-        <v>0.015657</v>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -23210,15 +23138,19 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>1,372,359</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -23244,18 +23176,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J227" s="5" t="n">
-        <v>0.15256</v>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>106.538916</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>131.710164</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -23291,14 +23221,10 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Operating Expenses total</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Legal settlement (Note 13)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -23319,11 +23245,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I228" s="5" t="n">
-        <v>0.196466</v>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J228" s="5" t="n">
-        <v>0.983422</v>
+        <v>0.25</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -23364,12 +23292,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt</t>
+          <t>Office, admin and rent</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -23393,18 +23321,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I229" s="5" t="n">
-        <v>0.02665</v>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" s="5" t="n">
+        <v>0.015657</v>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>0.127723</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -23440,12 +23366,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Loan receivable write-off (Note 13)</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -23475,12 +23401,10 @@
         </is>
       </c>
       <c r="J230" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.983422</v>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>-3.535976</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -23516,19 +23440,15 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Flow-through share premium</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -23554,13 +23474,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J231" s="5" t="n">
-        <v>0.002397</v>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>2.211</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -23596,17 +23516,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Loss and Comprehensive Loss for the Year</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -23629,16 +23549,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I232" s="5" t="n">
-        <v>-0.223116</v>
-      </c>
-      <c r="J232" s="5" t="n">
-        <v>-1.135819</v>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>0.063985</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -23674,17 +23596,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Loss Per Share – Basic and Diluted</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -23707,16 +23629,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I233" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J233" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002397</v>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>-0.012534</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -23752,19 +23674,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares Outstanding</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Loan receivable write-off (Note 13)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -23785,11 +23703,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I234" s="5" t="n">
-        <v>11.437156</v>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J234" s="5" t="n">
-        <v>23.596015</v>
+        <v>-0.15</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -23835,12 +23755,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Consulting fees (note 6)</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -23853,24 +23773,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G235" s="5" t="n">
-        <v>0.0525</v>
-      </c>
-      <c r="H235" s="5" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="I235" s="5" t="n">
-        <v>0.1425</v>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" s="5" t="n">
+        <v>-1.135819</v>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>-1.273525</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -23911,12 +23833,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Loss before other item</t>
+          <t>Loss per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -23924,27 +23846,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F236" s="5" t="n">
-        <v>-0.097496</v>
-      </c>
-      <c r="G236" s="5" t="n">
-        <v>-0.102151</v>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>-0.103195</v>
-      </c>
-      <c r="I236" s="5" t="n">
-        <v>-0.196466</v>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -23980,15 +23906,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -24009,18 +23939,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I237" s="5" t="n">
-        <v>0.02665</v>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" s="5" t="n">
+        <v>23.596015</v>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>106.538916</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -24056,17 +23984,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Consulting fees (Note 7)</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -24079,19 +24007,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G238" s="5" t="n">
-        <v>-0.092131</v>
-      </c>
-      <c r="H238" s="5" t="n">
-        <v>-0.103195</v>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I238" s="5" t="n">
-        <v>-0.223116</v>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1425</v>
+      </c>
+      <c r="J238" s="5" t="n">
+        <v>0.079613</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -24132,17 +24062,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Loss Per Share – Basic and Diluted</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -24150,24 +24080,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F239" s="5" t="n">
+        <v>0.008267</v>
       </c>
       <c r="G239" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.004773</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.004012</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012454</v>
+      </c>
+      <c r="J239" s="5" t="n">
+        <v>0.015657</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -24208,40 +24134,42 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares Outstanding</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F240" s="5" t="n">
-        <v>1.928658</v>
-      </c>
-      <c r="G240" s="5" t="n">
-        <v>1.928658</v>
-      </c>
-      <c r="H240" s="5" t="n">
-        <v>1.928658</v>
-      </c>
-      <c r="I240" s="5" t="n">
-        <v>11.437156</v>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" s="5" t="n">
+        <v>0.15256</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -24282,42 +24210,42 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Write-off of accounts payable</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating Expenses total</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="n">
+        <v>0.104859</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G241" s="5" t="n">
-        <v>0.01002</v>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I241" s="5" t="n">
+        <v>0.196466</v>
+      </c>
+      <c r="J241" s="5" t="n">
+        <v>0.983422</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -24358,39 +24286,37 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Consulting fees (note 6) $</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Loss on settlement of debt</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F242" s="5" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="G242" s="5" t="n">
-        <v>0.0525</v>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I242" s="5" t="n">
+        <v>0.02665</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -24436,29 +24362,29 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loan receivable write-off (Note 13)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F243" s="5" t="n">
-        <v>-0.097496</v>
-      </c>
-      <c r="G243" s="5" t="n">
-        <v>-0.092131</v>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -24470,10 +24396,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J243" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -24514,71 +24438,1845 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J244" s="5" t="n">
+        <v>0.002397</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Loss and Comprehensive Loss for the Year</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>-0.223116</v>
+      </c>
+      <c r="J245" s="5" t="n">
+        <v>-1.135819</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Loss Per Share – Basic and Diluted</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J246" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Common Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" s="5" t="n">
+        <v>11.437156</v>
+      </c>
+      <c r="J247" s="5" t="n">
+        <v>23.596015</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Consulting fees (note 6)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G248" s="5" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="H248" s="5" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Loss before other item</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="n">
+        <v>-0.097496</v>
+      </c>
+      <c r="G249" s="5" t="n">
+        <v>-0.102151</v>
+      </c>
+      <c r="H249" s="5" t="n">
+        <v>-0.103195</v>
+      </c>
+      <c r="I249" s="5" t="n">
+        <v>-0.196466</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
           <t>Other Item</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Loss on settlement of debt</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>0.02665</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G251" s="5" t="n">
+        <v>-0.092131</v>
+      </c>
+      <c r="H251" s="5" t="n">
+        <v>-0.103195</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>-0.223116</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Loss Per Share – Basic and Diluted</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G252" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="H252" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Common Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>1.928658</v>
+      </c>
+      <c r="G253" s="5" t="n">
+        <v>1.928658</v>
+      </c>
+      <c r="H253" s="5" t="n">
+        <v>1.928658</v>
+      </c>
+      <c r="I253" s="5" t="n">
+        <v>11.437156</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Write-off of accounts payable</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G254" s="5" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Consulting fees (note 6) $</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="G255" s="5" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>-0.097496</v>
+      </c>
+      <c r="G256" s="5" t="n">
+        <v>-0.092131</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Other Item</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>Loss Per Share – Basic and Diluted $</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F244" s="5" t="n">
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="n">
         <v>-5e-08</v>
       </c>
-      <c r="G244" s="5" t="n">
+      <c r="G257" s="5" t="n">
         <v>-4e-08</v>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P244" t="inlineStr">
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>For the years ended January</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Consulting fees and salary $ 48,000 $</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" s="5" t="n">
+        <v>0.048289</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Office 502</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="n">
+        <v>0.001954</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Professional fees 13,424</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="n">
+        <v>0.017011</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Shareholder relations 5,238</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" s="5" t="n">
+        <v>0.005182</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees 26,969</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="n">
+        <v>0.032423</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Write-off of exploration and evaluation assets (note 5) -</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" s="5" t="n">
+        <v>-0.046175</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year (94,133)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="n">
+        <v>-0.151034</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Loss Per Share – Basic and Diluted $ (0.01) $</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Common Shares Outstanding 18,512,657</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="n">
+        <v>16.762437</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
         <is>
           <t>-</t>
         </is>
